--- a/매출손익현황.xlsx
+++ b/매출손익현황.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="252">
   <si>
     <t>지중No</t>
   </si>
@@ -137,6 +137,9 @@
     <t>JY25-258</t>
   </si>
   <si>
+    <t>JY25-260</t>
+  </si>
+  <si>
     <t>JY26-001</t>
   </si>
   <si>
@@ -233,6 +236,12 @@
     <t>JY26-057</t>
   </si>
   <si>
+    <t>JY26-059</t>
+  </si>
+  <si>
+    <t>JY26-066</t>
+  </si>
+  <si>
     <t>MY25-002</t>
   </si>
   <si>
@@ -482,6 +491,9 @@
     <t>초평지구 가로등 2개소 인입접속공사</t>
   </si>
   <si>
+    <t>안양동 413-1 (주)대영플러스 일반용(갑)저압 120Kw 신설 외 1</t>
+  </si>
+  <si>
     <t>평촌동895 한국환경공단 210kW 신설</t>
   </si>
   <si>
@@ -576,6 +588,12 @@
   </si>
   <si>
     <t>고천동 526-7 이인성 저압 35kw 신설</t>
+  </si>
+  <si>
+    <t>고천동528 박희상 저압 신설</t>
+  </si>
+  <si>
+    <t>초평동622-2 이원섭 저압 신설</t>
   </si>
   <si>
     <t>고양외고 여자기숙사 간이스프링쿨러 설치공사</t>
@@ -1224,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet0.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P346"/>
+  <dimension ref="A1:P355"/>
   <cols>
     <col min="1" max="1" width="11.43" customWidth="1"/>
     <col min="2" max="2" width="28.57" customWidth="1"/>
@@ -1249,49 +1267,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.5" customHeight="1">
@@ -1317,10 +1335,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>0.00</v>
@@ -1403,10 +1421,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>0.00</v>
@@ -1489,10 +1507,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>0.00</v>
@@ -1575,10 +1593,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>0.00</v>
@@ -1661,10 +1679,10 @@
         <v>5</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.00</v>
@@ -1750,7 +1768,7 @@
         <v/>
       </c>
       <c r="C18" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>0.00</v>
@@ -1833,10 +1851,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D21" s="15" t="n">
         <v>274329.78</v>
@@ -1919,10 +1937,10 @@
         <v>8</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>6824961.05</v>
@@ -2005,10 +2023,10 @@
         <v>9</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D27" s="15" t="n">
         <v>181803.40</v>
@@ -2091,10 +2109,10 @@
         <v>10</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>0.00</v>
@@ -2177,10 +2195,10 @@
         <v>11</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D33" s="15" t="n">
         <v>0.00</v>
@@ -2263,10 +2281,10 @@
         <v>12</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>0.00</v>
@@ -2349,10 +2367,10 @@
         <v>13</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D39" s="15" t="n">
         <v>0.00</v>
@@ -2435,10 +2453,10 @@
         <v>14</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>0.00</v>
@@ -2521,10 +2539,10 @@
         <v>15</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D45" s="15" t="n">
         <v>0.00</v>
@@ -2607,10 +2625,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D48" s="16" t="n">
         <v>0.00</v>
@@ -2693,10 +2711,10 @@
         <v>17</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D51" s="15" t="n">
         <v>0.00</v>
@@ -2779,10 +2797,10 @@
         <v>18</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D54" s="16" t="n">
         <v>0.00</v>
@@ -2865,10 +2883,10 @@
         <v>19</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D57" s="15" t="n">
         <v>0.00</v>
@@ -2951,10 +2969,10 @@
         <v>20</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>0.00</v>
@@ -3037,10 +3055,10 @@
         <v>21</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D63" s="15" t="n">
         <v>0.00</v>
@@ -3058,7 +3076,7 @@
         <v>8926943.45</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>0.00</v>
+        <v>1575342.96</v>
       </c>
       <c r="J63" s="15" t="n">
         <v>0.00</v>
@@ -3079,7 +3097,7 @@
         <v>0.00</v>
       </c>
       <c r="P63" s="15" t="n">
-        <v>8926943.45</v>
+        <v>10502286.41</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="16.5" customHeight="1">
@@ -3123,10 +3141,10 @@
         <v>22</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D66" s="16" t="n">
         <v>0.00</v>
@@ -3209,10 +3227,10 @@
         <v>23</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D69" s="15" t="n">
         <v>0.00</v>
@@ -3295,10 +3313,10 @@
         <v>24</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D72" s="16" t="n">
         <v>0.00</v>
@@ -3381,10 +3399,10 @@
         <v>25</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D75" s="15" t="n">
         <v>0.00</v>
@@ -3467,10 +3485,10 @@
         <v>26</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D78" s="16" t="n">
         <v>0.00</v>
@@ -3553,10 +3571,10 @@
         <v>27</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D81" s="15" t="n">
         <v>0.00</v>
@@ -3639,10 +3657,10 @@
         <v>28</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D84" s="16" t="n">
         <v>0.00</v>
@@ -3725,10 +3743,10 @@
         <v>29</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D87" s="15" t="n">
         <v>6824518.80</v>
@@ -3811,10 +3829,10 @@
         <v>30</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D90" s="16" t="n">
         <v>0.00</v>
@@ -3897,10 +3915,10 @@
         <v>31</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D93" s="15" t="n">
         <v>0.00</v>
@@ -3983,10 +4001,10 @@
         <v>32</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D96" s="16" t="n">
         <v>1215867.69</v>
@@ -4069,10 +4087,10 @@
         <v>33</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D99" s="15" t="n">
         <v>0.00</v>
@@ -4155,10 +4173,10 @@
         <v>34</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D102" s="16" t="n">
         <v>0.00</v>
@@ -4241,10 +4259,10 @@
         <v>35</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D105" s="15" t="n">
         <v>4873420.45</v>
@@ -4327,10 +4345,10 @@
         <v>36</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D108" s="16" t="n">
         <v>1106423.27</v>
@@ -4413,10 +4431,10 @@
         <v>37</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D111" s="15" t="n">
         <v>0.00</v>
@@ -4499,10 +4517,10 @@
         <v>38</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D114" s="16" t="n">
         <v>0.00</v>
@@ -4585,10 +4603,10 @@
         <v>39</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D117" s="15" t="n">
         <v>0.00</v>
@@ -4671,10 +4689,10 @@
         <v>40</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D120" s="16" t="n">
         <v>0.00</v>
@@ -4757,10 +4775,10 @@
         <v>41</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D123" s="15" t="n">
         <v>283322.30</v>
@@ -4843,10 +4861,10 @@
         <v>42</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D126" s="16" t="n">
         <v>0.00</v>
@@ -4858,13 +4876,13 @@
         <v>0.00</v>
       </c>
       <c r="G126" s="16" t="n">
-        <v>12087832.50</v>
+        <v>0.00</v>
       </c>
       <c r="H126" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="I126" s="16" t="n">
-        <v>0.00</v>
+        <v>4035280.68</v>
       </c>
       <c r="J126" s="16" t="n">
         <v>0.00</v>
@@ -4885,7 +4903,7 @@
         <v>0.00</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>12087832.50</v>
+        <v>4035280.68</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="16.5" customHeight="1">
@@ -4929,13 +4947,13 @@
         <v>43</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D129" s="15" t="n">
-        <v>181803.40</v>
+        <v>0.00</v>
       </c>
       <c r="E129" s="15" t="n">
         <v>0.00</v>
@@ -4944,7 +4962,7 @@
         <v>0.00</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>0.00</v>
+        <v>12087832.50</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>0.00</v>
@@ -4971,7 +4989,7 @@
         <v>0.00</v>
       </c>
       <c r="P129" s="15" t="n">
-        <v>181803.40</v>
+        <v>12087832.50</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="16.5" customHeight="1">
@@ -5015,13 +5033,13 @@
         <v>44</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D132" s="16" t="n">
-        <v>788788.41</v>
+        <v>181803.40</v>
       </c>
       <c r="E132" s="16" t="n">
         <v>0.00</v>
@@ -5057,7 +5075,7 @@
         <v>0.00</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>788788.41</v>
+        <v>181803.40</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="16.5" customHeight="1">
@@ -5101,19 +5119,19 @@
         <v>45</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D135" s="15" t="n">
-        <v>0.00</v>
+        <v>788788.41</v>
       </c>
       <c r="E135" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="F135" s="15" t="n">
-        <v>599108.11</v>
+        <v>0.00</v>
       </c>
       <c r="G135" s="15" t="n">
         <v>0.00</v>
@@ -5143,7 +5161,7 @@
         <v>0.00</v>
       </c>
       <c r="P135" s="15" t="n">
-        <v>599108.11</v>
+        <v>788788.41</v>
       </c>
     </row>
     <row r="136" spans="1:16" ht="16.5" customHeight="1">
@@ -5187,19 +5205,19 @@
         <v>46</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D138" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="E138" s="16" t="n">
-        <v>195625.92</v>
+        <v>0.00</v>
       </c>
       <c r="F138" s="16" t="n">
-        <v>0.00</v>
+        <v>599108.11</v>
       </c>
       <c r="G138" s="16" t="n">
         <v>0.00</v>
@@ -5229,7 +5247,7 @@
         <v>0.00</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>195625.92</v>
+        <v>599108.11</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="16.5" customHeight="1">
@@ -5273,19 +5291,19 @@
         <v>47</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D141" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>0.00</v>
+        <v>195625.92</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>65578.87</v>
+        <v>0.00</v>
       </c>
       <c r="G141" s="15" t="n">
         <v>0.00</v>
@@ -5315,7 +5333,7 @@
         <v>0.00</v>
       </c>
       <c r="P141" s="15" t="n">
-        <v>65578.87</v>
+        <v>195625.92</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="16.5" customHeight="1">
@@ -5359,19 +5377,19 @@
         <v>48</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D144" s="16" t="n">
-        <v>41159969.18</v>
+        <v>0.00</v>
       </c>
       <c r="E144" s="16" t="n">
-        <v>52919960.37</v>
+        <v>0.00</v>
       </c>
       <c r="F144" s="16" t="n">
-        <v>0.00</v>
+        <v>65578.87</v>
       </c>
       <c r="G144" s="16" t="n">
         <v>0.00</v>
@@ -5401,7 +5419,7 @@
         <v>0.00</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>94079929.55</v>
+        <v>65578.87</v>
       </c>
     </row>
     <row r="145" spans="1:16" ht="16.5" customHeight="1">
@@ -5445,28 +5463,28 @@
         <v>49</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D147" s="15" t="n">
-        <v>0.00</v>
+        <v>41159969.18</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>0.00</v>
+        <v>52919960.37</v>
       </c>
       <c r="F147" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="G147" s="15" t="n">
-        <v>17062682.47</v>
+        <v>0.00</v>
       </c>
       <c r="H147" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>898035.92</v>
+        <v>0.00</v>
       </c>
       <c r="J147" s="15" t="n">
         <v>0.00</v>
@@ -5487,7 +5505,7 @@
         <v>0.00</v>
       </c>
       <c r="P147" s="15" t="n">
-        <v>17960718.39</v>
+        <v>94079929.55</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="16.5" customHeight="1">
@@ -5531,28 +5549,28 @@
         <v>50</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D150" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="E150" s="16" t="n">
-        <v>508343.65</v>
+        <v>0.00</v>
       </c>
       <c r="F150" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="G150" s="16" t="n">
-        <v>0.00</v>
+        <v>17062682.47</v>
       </c>
       <c r="H150" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="I150" s="16" t="n">
-        <v>0.00</v>
+        <v>898035.92</v>
       </c>
       <c r="J150" s="16" t="n">
         <v>0.00</v>
@@ -5573,7 +5591,7 @@
         <v>0.00</v>
       </c>
       <c r="P150" s="16" t="n">
-        <v>508343.65</v>
+        <v>17960718.39</v>
       </c>
     </row>
     <row r="151" spans="1:16" ht="16.5" customHeight="1">
@@ -5617,25 +5635,25 @@
         <v>51</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D153" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>0.00</v>
+        <v>508343.65</v>
       </c>
       <c r="F153" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="G153" s="15" t="n">
-        <v>2866492.64</v>
+        <v>0.00</v>
       </c>
       <c r="H153" s="15" t="n">
-        <v>716623.16</v>
+        <v>0.00</v>
       </c>
       <c r="I153" s="15" t="n">
         <v>0.00</v>
@@ -5659,7 +5677,7 @@
         <v>0.00</v>
       </c>
       <c r="P153" s="15" t="n">
-        <v>3583115.80</v>
+        <v>508343.65</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="16.5" customHeight="1">
@@ -5703,10 +5721,10 @@
         <v>52</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D156" s="16" t="n">
         <v>0.00</v>
@@ -5718,10 +5736,10 @@
         <v>0.00</v>
       </c>
       <c r="G156" s="16" t="n">
-        <v>0.00</v>
+        <v>2866492.64</v>
       </c>
       <c r="H156" s="16" t="n">
-        <v>218199.31</v>
+        <v>716623.16</v>
       </c>
       <c r="I156" s="16" t="n">
         <v>0.00</v>
@@ -5745,7 +5763,7 @@
         <v>0.00</v>
       </c>
       <c r="P156" s="16" t="n">
-        <v>218199.31</v>
+        <v>3583115.80</v>
       </c>
     </row>
     <row r="157" spans="1:16" ht="16.5" customHeight="1">
@@ -5789,10 +5807,10 @@
         <v>53</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D159" s="15" t="n">
         <v>0.00</v>
@@ -5807,7 +5825,7 @@
         <v>0.00</v>
       </c>
       <c r="H159" s="15" t="n">
-        <v>564671.38</v>
+        <v>218199.31</v>
       </c>
       <c r="I159" s="15" t="n">
         <v>0.00</v>
@@ -5831,7 +5849,7 @@
         <v>0.00</v>
       </c>
       <c r="P159" s="15" t="n">
-        <v>564671.38</v>
+        <v>218199.31</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="16.5" customHeight="1">
@@ -5875,10 +5893,10 @@
         <v>54</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D162" s="16" t="n">
         <v>0.00</v>
@@ -5887,13 +5905,13 @@
         <v>0.00</v>
       </c>
       <c r="F162" s="16" t="n">
-        <v>183494.94</v>
+        <v>0.00</v>
       </c>
       <c r="G162" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="H162" s="16" t="n">
-        <v>0.00</v>
+        <v>564671.38</v>
       </c>
       <c r="I162" s="16" t="n">
         <v>0.00</v>
@@ -5917,7 +5935,7 @@
         <v>0.00</v>
       </c>
       <c r="P162" s="16" t="n">
-        <v>183494.94</v>
+        <v>564671.38</v>
       </c>
     </row>
     <row r="163" spans="1:16" ht="16.5" customHeight="1">
@@ -5961,10 +5979,10 @@
         <v>55</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D165" s="15" t="n">
         <v>0.00</v>
@@ -5973,7 +5991,7 @@
         <v>0.00</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>121347.78</v>
+        <v>183494.94</v>
       </c>
       <c r="G165" s="15" t="n">
         <v>0.00</v>
@@ -6003,7 +6021,7 @@
         <v>0.00</v>
       </c>
       <c r="P165" s="15" t="n">
-        <v>121347.78</v>
+        <v>183494.94</v>
       </c>
     </row>
     <row r="166" spans="1:16" ht="16.5" customHeight="1">
@@ -6047,10 +6065,10 @@
         <v>56</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D168" s="16" t="n">
         <v>0.00</v>
@@ -6059,10 +6077,10 @@
         <v>0.00</v>
       </c>
       <c r="F168" s="16" t="n">
-        <v>0.00</v>
+        <v>121347.78</v>
       </c>
       <c r="G168" s="16" t="n">
-        <v>61029.83</v>
+        <v>0.00</v>
       </c>
       <c r="H168" s="16" t="n">
         <v>0.00</v>
@@ -6089,7 +6107,7 @@
         <v>0.00</v>
       </c>
       <c r="P168" s="16" t="n">
-        <v>61029.83</v>
+        <v>121347.78</v>
       </c>
     </row>
     <row r="169" spans="1:16" ht="16.5" customHeight="1">
@@ -6133,10 +6151,10 @@
         <v>57</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D171" s="15" t="n">
         <v>0.00</v>
@@ -6148,7 +6166,7 @@
         <v>0.00</v>
       </c>
       <c r="G171" s="15" t="n">
-        <v>1040490.23</v>
+        <v>61029.83</v>
       </c>
       <c r="H171" s="15" t="n">
         <v>0.00</v>
@@ -6175,7 +6193,7 @@
         <v>0.00</v>
       </c>
       <c r="P171" s="15" t="n">
-        <v>1040490.23</v>
+        <v>61029.83</v>
       </c>
     </row>
     <row r="172" spans="1:16" ht="16.5" customHeight="1">
@@ -6219,10 +6237,10 @@
         <v>58</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D174" s="16" t="n">
         <v>0.00</v>
@@ -6234,7 +6252,7 @@
         <v>0.00</v>
       </c>
       <c r="G174" s="16" t="n">
-        <v>232318.79</v>
+        <v>1040490.23</v>
       </c>
       <c r="H174" s="16" t="n">
         <v>0.00</v>
@@ -6261,7 +6279,7 @@
         <v>0.00</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>232318.79</v>
+        <v>1040490.23</v>
       </c>
     </row>
     <row r="175" spans="1:16" ht="16.5" customHeight="1">
@@ -6305,10 +6323,10 @@
         <v>59</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D177" s="15" t="n">
         <v>0.00</v>
@@ -6320,10 +6338,10 @@
         <v>0.00</v>
       </c>
       <c r="G177" s="15" t="n">
-        <v>0.00</v>
+        <v>232318.79</v>
       </c>
       <c r="H177" s="15" t="n">
-        <v>137269.82</v>
+        <v>0.00</v>
       </c>
       <c r="I177" s="15" t="n">
         <v>0.00</v>
@@ -6347,7 +6365,7 @@
         <v>0.00</v>
       </c>
       <c r="P177" s="15" t="n">
-        <v>137269.82</v>
+        <v>232318.79</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="16.5" customHeight="1">
@@ -6391,10 +6409,10 @@
         <v>60</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D180" s="16" t="n">
         <v>0.00</v>
@@ -6406,10 +6424,10 @@
         <v>0.00</v>
       </c>
       <c r="G180" s="16" t="n">
-        <v>18930086.24</v>
+        <v>0.00</v>
       </c>
       <c r="H180" s="16" t="n">
-        <v>1314589.32</v>
+        <v>137269.82</v>
       </c>
       <c r="I180" s="16" t="n">
         <v>0.00</v>
@@ -6433,7 +6451,7 @@
         <v>0.00</v>
       </c>
       <c r="P180" s="16" t="n">
-        <v>20244675.56</v>
+        <v>137269.82</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="16.5" customHeight="1">
@@ -6477,10 +6495,10 @@
         <v>61</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D183" s="15" t="n">
         <v>0.00</v>
@@ -6492,10 +6510,10 @@
         <v>0.00</v>
       </c>
       <c r="G183" s="15" t="n">
-        <v>0.00</v>
+        <v>18930086.24</v>
       </c>
       <c r="H183" s="15" t="n">
-        <v>67810.92</v>
+        <v>1314589.32</v>
       </c>
       <c r="I183" s="15" t="n">
         <v>0.00</v>
@@ -6519,7 +6537,7 @@
         <v>0.00</v>
       </c>
       <c r="P183" s="15" t="n">
-        <v>67810.92</v>
+        <v>20244675.56</v>
       </c>
     </row>
     <row r="184" spans="1:16" ht="16.5" customHeight="1">
@@ -6563,10 +6581,10 @@
         <v>62</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D186" s="16" t="n">
         <v>0.00</v>
@@ -6581,7 +6599,7 @@
         <v>0.00</v>
       </c>
       <c r="H186" s="16" t="n">
-        <v>203883.27</v>
+        <v>67810.92</v>
       </c>
       <c r="I186" s="16" t="n">
         <v>0.00</v>
@@ -6605,7 +6623,7 @@
         <v>0.00</v>
       </c>
       <c r="P186" s="16" t="n">
-        <v>203883.27</v>
+        <v>67810.92</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="16.5" customHeight="1">
@@ -6649,10 +6667,10 @@
         <v>63</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D189" s="15" t="n">
         <v>0.00</v>
@@ -6667,7 +6685,7 @@
         <v>0.00</v>
       </c>
       <c r="H189" s="15" t="n">
-        <v>567348.57</v>
+        <v>203883.27</v>
       </c>
       <c r="I189" s="15" t="n">
         <v>0.00</v>
@@ -6691,7 +6709,7 @@
         <v>0.00</v>
       </c>
       <c r="P189" s="15" t="n">
-        <v>567348.57</v>
+        <v>203883.27</v>
       </c>
     </row>
     <row r="190" spans="1:16" ht="16.5" customHeight="1">
@@ -6735,10 +6753,10 @@
         <v>64</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D192" s="16" t="n">
         <v>0.00</v>
@@ -6753,10 +6771,10 @@
         <v>0.00</v>
       </c>
       <c r="H192" s="16" t="n">
-        <v>0.00</v>
+        <v>567348.57</v>
       </c>
       <c r="I192" s="16" t="n">
-        <v>405701.07</v>
+        <v>0.00</v>
       </c>
       <c r="J192" s="16" t="n">
         <v>0.00</v>
@@ -6777,7 +6795,7 @@
         <v>0.00</v>
       </c>
       <c r="P192" s="16" t="n">
-        <v>405701.07</v>
+        <v>567348.57</v>
       </c>
     </row>
     <row r="193" spans="1:16" ht="16.5" customHeight="1">
@@ -6821,10 +6839,10 @@
         <v>65</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D195" s="15" t="n">
         <v>0.00</v>
@@ -6842,7 +6860,7 @@
         <v>0.00</v>
       </c>
       <c r="I195" s="15" t="n">
-        <v>9903715.08</v>
+        <v>405701.07</v>
       </c>
       <c r="J195" s="15" t="n">
         <v>0.00</v>
@@ -6863,7 +6881,7 @@
         <v>0.00</v>
       </c>
       <c r="P195" s="15" t="n">
-        <v>9903715.08</v>
+        <v>405701.07</v>
       </c>
     </row>
     <row r="196" spans="1:16" ht="16.5" customHeight="1">
@@ -6907,10 +6925,10 @@
         <v>66</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D198" s="16" t="n">
         <v>0.00</v>
@@ -6925,10 +6943,10 @@
         <v>0.00</v>
       </c>
       <c r="H198" s="16" t="n">
-        <v>9234671.95</v>
+        <v>0.00</v>
       </c>
       <c r="I198" s="16" t="n">
-        <v>1629647.99</v>
+        <v>9903715.08</v>
       </c>
       <c r="J198" s="16" t="n">
         <v>0.00</v>
@@ -6949,7 +6967,7 @@
         <v>0.00</v>
       </c>
       <c r="P198" s="16" t="n">
-        <v>10864319.94</v>
+        <v>9903715.08</v>
       </c>
     </row>
     <row r="199" spans="1:16" ht="16.5" customHeight="1">
@@ -6993,10 +7011,10 @@
         <v>67</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D201" s="15" t="n">
         <v>0.00</v>
@@ -7011,10 +7029,10 @@
         <v>0.00</v>
       </c>
       <c r="H201" s="15" t="n">
-        <v>137269.82</v>
+        <v>9234671.95</v>
       </c>
       <c r="I201" s="15" t="n">
-        <v>0.00</v>
+        <v>1629647.99</v>
       </c>
       <c r="J201" s="15" t="n">
         <v>0.00</v>
@@ -7035,7 +7053,7 @@
         <v>0.00</v>
       </c>
       <c r="P201" s="15" t="n">
-        <v>137269.82</v>
+        <v>10864319.94</v>
       </c>
     </row>
     <row r="202" spans="1:16" ht="16.5" customHeight="1">
@@ -7079,10 +7097,10 @@
         <v>68</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D204" s="16" t="n">
         <v>0.00</v>
@@ -7097,7 +7115,7 @@
         <v>0.00</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>199314.38</v>
+        <v>137269.82</v>
       </c>
       <c r="I204" s="16" t="n">
         <v>0.00</v>
@@ -7121,7 +7139,7 @@
         <v>0.00</v>
       </c>
       <c r="P204" s="16" t="n">
-        <v>199314.38</v>
+        <v>137269.82</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="16.5" customHeight="1">
@@ -7165,10 +7183,10 @@
         <v>69</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D207" s="15" t="n">
         <v>0.00</v>
@@ -7183,10 +7201,10 @@
         <v>0.00</v>
       </c>
       <c r="H207" s="15" t="n">
-        <v>0.00</v>
+        <v>199314.38</v>
       </c>
       <c r="I207" s="15" t="n">
-        <v>6256891.48</v>
+        <v>0.00</v>
       </c>
       <c r="J207" s="15" t="n">
         <v>0.00</v>
@@ -7207,7 +7225,7 @@
         <v>0.00</v>
       </c>
       <c r="P207" s="15" t="n">
-        <v>6256891.48</v>
+        <v>199314.38</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="16.5" customHeight="1">
@@ -7251,10 +7269,10 @@
         <v>70</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D210" s="16" t="n">
         <v>0.00</v>
@@ -7272,7 +7290,7 @@
         <v>0.00</v>
       </c>
       <c r="I210" s="16" t="n">
-        <v>17285.71</v>
+        <v>6256891.48</v>
       </c>
       <c r="J210" s="16" t="n">
         <v>0.00</v>
@@ -7293,7 +7311,7 @@
         <v>0.00</v>
       </c>
       <c r="P210" s="16" t="n">
-        <v>17285.71</v>
+        <v>6256891.48</v>
       </c>
     </row>
     <row r="211" spans="1:16" ht="16.5" customHeight="1">
@@ -7337,10 +7355,10 @@
         <v>71</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D213" s="15" t="n">
         <v>0.00</v>
@@ -7355,10 +7373,10 @@
         <v>0.00</v>
       </c>
       <c r="H213" s="15" t="n">
-        <v>203883.27</v>
+        <v>0.00</v>
       </c>
       <c r="I213" s="15" t="n">
-        <v>0.00</v>
+        <v>17285.71</v>
       </c>
       <c r="J213" s="15" t="n">
         <v>0.00</v>
@@ -7379,7 +7397,7 @@
         <v>0.00</v>
       </c>
       <c r="P213" s="15" t="n">
-        <v>203883.27</v>
+        <v>17285.71</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="16.5" customHeight="1">
@@ -7423,10 +7441,10 @@
         <v>72</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D216" s="16" t="n">
         <v>0.00</v>
@@ -7441,10 +7459,10 @@
         <v>0.00</v>
       </c>
       <c r="H216" s="16" t="n">
-        <v>0.00</v>
+        <v>203883.27</v>
       </c>
       <c r="I216" s="16" t="n">
-        <v>203883.27</v>
+        <v>0.00</v>
       </c>
       <c r="J216" s="16" t="n">
         <v>0.00</v>
@@ -7509,10 +7527,10 @@
         <v>73</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D219" s="15" t="n">
         <v>0.00</v>
@@ -7530,7 +7548,7 @@
         <v>0.00</v>
       </c>
       <c r="I219" s="15" t="n">
-        <v>925466.57</v>
+        <v>203883.27</v>
       </c>
       <c r="J219" s="15" t="n">
         <v>0.00</v>
@@ -7551,7 +7569,7 @@
         <v>0.00</v>
       </c>
       <c r="P219" s="15" t="n">
-        <v>925466.57</v>
+        <v>203883.27</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="16.5" customHeight="1">
@@ -7595,16 +7613,16 @@
         <v>74</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D222" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="E222" s="16" t="n">
-        <v>203561619.00</v>
+        <v>0.00</v>
       </c>
       <c r="F222" s="16" t="n">
         <v>0.00</v>
@@ -7616,7 +7634,7 @@
         <v>0.00</v>
       </c>
       <c r="I222" s="16" t="n">
-        <v>0.00</v>
+        <v>925466.57</v>
       </c>
       <c r="J222" s="16" t="n">
         <v>0.00</v>
@@ -7637,7 +7655,7 @@
         <v>0.00</v>
       </c>
       <c r="P222" s="16" t="n">
-        <v>203561619.00</v>
+        <v>925466.57</v>
       </c>
     </row>
     <row r="223" spans="1:16" ht="16.5" customHeight="1">
@@ -7681,16 +7699,16 @@
         <v>75</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D225" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="E225" s="15" t="n">
-        <v>127171014.53</v>
+        <v>0.00</v>
       </c>
       <c r="F225" s="15" t="n">
         <v>0.00</v>
@@ -7702,7 +7720,7 @@
         <v>0.00</v>
       </c>
       <c r="I225" s="15" t="n">
-        <v>0.00</v>
+        <v>507687.92</v>
       </c>
       <c r="J225" s="15" t="n">
         <v>0.00</v>
@@ -7723,7 +7741,7 @@
         <v>0.00</v>
       </c>
       <c r="P225" s="15" t="n">
-        <v>127171014.53</v>
+        <v>507687.92</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="16.5" customHeight="1">
@@ -7767,16 +7785,16 @@
         <v>76</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D228" s="16" t="n">
-        <v>120909900.00</v>
+        <v>0.00</v>
       </c>
       <c r="E228" s="16" t="n">
-        <v>44720100.00</v>
+        <v>0.00</v>
       </c>
       <c r="F228" s="16" t="n">
         <v>0.00</v>
@@ -7788,7 +7806,7 @@
         <v>0.00</v>
       </c>
       <c r="I228" s="16" t="n">
-        <v>0.00</v>
+        <v>835486.55</v>
       </c>
       <c r="J228" s="16" t="n">
         <v>0.00</v>
@@ -7809,7 +7827,7 @@
         <v>0.00</v>
       </c>
       <c r="P228" s="16" t="n">
-        <v>165630000.00</v>
+        <v>835486.55</v>
       </c>
     </row>
     <row r="229" spans="1:16" ht="16.5" customHeight="1">
@@ -7853,16 +7871,16 @@
         <v>77</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D231" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="E231" s="15" t="n">
-        <v>3784091.75</v>
+        <v>203561619.00</v>
       </c>
       <c r="F231" s="15" t="n">
         <v>0.00</v>
@@ -7895,7 +7913,7 @@
         <v>0.00</v>
       </c>
       <c r="P231" s="15" t="n">
-        <v>3784091.75</v>
+        <v>203561619.00</v>
       </c>
     </row>
     <row r="232" spans="1:16" ht="16.5" customHeight="1">
@@ -7939,19 +7957,19 @@
         <v>78</v>
       </c>
       <c r="B234" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D234" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="E234" s="16" t="n">
-        <v>0.00</v>
+        <v>127171014.53</v>
       </c>
       <c r="F234" s="16" t="n">
-        <v>18500000.00</v>
+        <v>0.00</v>
       </c>
       <c r="G234" s="16" t="n">
         <v>0.00</v>
@@ -7981,7 +7999,7 @@
         <v>0.00</v>
       </c>
       <c r="P234" s="16" t="n">
-        <v>18500000.00</v>
+        <v>127171014.53</v>
       </c>
     </row>
     <row r="235" spans="1:16" ht="16.5" customHeight="1">
@@ -8025,16 +8043,16 @@
         <v>79</v>
       </c>
       <c r="B237" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D237" s="15" t="n">
-        <v>0.00</v>
+        <v>120909900.00</v>
       </c>
       <c r="E237" s="15" t="n">
-        <v>2076372.55</v>
+        <v>44720100.00</v>
       </c>
       <c r="F237" s="15" t="n">
         <v>0.00</v>
@@ -8067,7 +8085,7 @@
         <v>0.00</v>
       </c>
       <c r="P237" s="15" t="n">
-        <v>2076372.55</v>
+        <v>165630000.00</v>
       </c>
     </row>
     <row r="238" spans="1:16" ht="16.5" customHeight="1">
@@ -8111,16 +8129,16 @@
         <v>80</v>
       </c>
       <c r="B240" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D240" s="16" t="n">
-        <v>5515126.23</v>
+        <v>0.00</v>
       </c>
       <c r="E240" s="16" t="n">
-        <v>0.00</v>
+        <v>3784091.75</v>
       </c>
       <c r="F240" s="16" t="n">
         <v>0.00</v>
@@ -8153,7 +8171,7 @@
         <v>0.00</v>
       </c>
       <c r="P240" s="16" t="n">
-        <v>5515126.23</v>
+        <v>3784091.75</v>
       </c>
     </row>
     <row r="241" spans="1:16" ht="16.5" customHeight="1">
@@ -8197,10 +8215,10 @@
         <v>81</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D243" s="15" t="n">
         <v>0.00</v>
@@ -8209,10 +8227,10 @@
         <v>0.00</v>
       </c>
       <c r="F243" s="15" t="n">
-        <v>0.00</v>
+        <v>18500000.00</v>
       </c>
       <c r="G243" s="15" t="n">
-        <v>5582787.78</v>
+        <v>0.00</v>
       </c>
       <c r="H243" s="15" t="n">
         <v>0.00</v>
@@ -8239,7 +8257,7 @@
         <v>0.00</v>
       </c>
       <c r="P243" s="15" t="n">
-        <v>5582787.78</v>
+        <v>18500000.00</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="16.5" customHeight="1">
@@ -8283,16 +8301,16 @@
         <v>82</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D246" s="16" t="n">
-        <v>2530035.20</v>
+        <v>0.00</v>
       </c>
       <c r="E246" s="16" t="n">
-        <v>7200869.40</v>
+        <v>2076372.55</v>
       </c>
       <c r="F246" s="16" t="n">
         <v>0.00</v>
@@ -8325,7 +8343,7 @@
         <v>0.00</v>
       </c>
       <c r="P246" s="16" t="n">
-        <v>9730904.60</v>
+        <v>2076372.55</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="16.5" customHeight="1">
@@ -8369,19 +8387,19 @@
         <v>83</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D249" s="15" t="n">
-        <v>0.00</v>
+        <v>5515126.23</v>
       </c>
       <c r="E249" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="F249" s="15" t="n">
-        <v>4960679.96</v>
+        <v>0.00</v>
       </c>
       <c r="G249" s="15" t="n">
         <v>0.00</v>
@@ -8411,7 +8429,7 @@
         <v>0.00</v>
       </c>
       <c r="P249" s="15" t="n">
-        <v>4960679.96</v>
+        <v>5515126.23</v>
       </c>
     </row>
     <row r="250" spans="1:16" ht="16.5" customHeight="1">
@@ -8455,13 +8473,13 @@
         <v>84</v>
       </c>
       <c r="B252" s="12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D252" s="16" t="n">
-        <v>22888437.30</v>
+        <v>0.00</v>
       </c>
       <c r="E252" s="16" t="n">
         <v>0.00</v>
@@ -8470,7 +8488,7 @@
         <v>0.00</v>
       </c>
       <c r="G252" s="16" t="n">
-        <v>0.00</v>
+        <v>5582787.78</v>
       </c>
       <c r="H252" s="16" t="n">
         <v>0.00</v>
@@ -8497,7 +8515,7 @@
         <v>0.00</v>
       </c>
       <c r="P252" s="16" t="n">
-        <v>22888437.30</v>
+        <v>5582787.78</v>
       </c>
     </row>
     <row r="253" spans="1:16" ht="16.5" customHeight="1">
@@ -8541,16 +8559,16 @@
         <v>85</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D255" s="15" t="n">
-        <v>0.00</v>
+        <v>2530035.20</v>
       </c>
       <c r="E255" s="15" t="n">
-        <v>847087.63</v>
+        <v>7200869.40</v>
       </c>
       <c r="F255" s="15" t="n">
         <v>0.00</v>
@@ -8583,7 +8601,7 @@
         <v>0.00</v>
       </c>
       <c r="P255" s="15" t="n">
-        <v>847087.63</v>
+        <v>9730904.60</v>
       </c>
     </row>
     <row r="256" spans="1:16" ht="16.5" customHeight="1">
@@ -8627,10 +8645,10 @@
         <v>86</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D258" s="16" t="n">
         <v>0.00</v>
@@ -8639,7 +8657,7 @@
         <v>0.00</v>
       </c>
       <c r="F258" s="16" t="n">
-        <v>0.00</v>
+        <v>4960679.96</v>
       </c>
       <c r="G258" s="16" t="n">
         <v>0.00</v>
@@ -8648,7 +8666,7 @@
         <v>0.00</v>
       </c>
       <c r="I258" s="16" t="n">
-        <v>1131124.74</v>
+        <v>0.00</v>
       </c>
       <c r="J258" s="16" t="n">
         <v>0.00</v>
@@ -8669,7 +8687,7 @@
         <v>0.00</v>
       </c>
       <c r="P258" s="16" t="n">
-        <v>1131124.74</v>
+        <v>4960679.96</v>
       </c>
     </row>
     <row r="259" spans="1:16" ht="16.5" customHeight="1">
@@ -8713,13 +8731,13 @@
         <v>87</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D261" s="15" t="n">
-        <v>0.00</v>
+        <v>22888437.30</v>
       </c>
       <c r="E261" s="15" t="n">
         <v>0.00</v>
@@ -8731,7 +8749,7 @@
         <v>0.00</v>
       </c>
       <c r="H261" s="15" t="n">
-        <v>2425416.39</v>
+        <v>0.00</v>
       </c>
       <c r="I261" s="15" t="n">
         <v>0.00</v>
@@ -8755,7 +8773,7 @@
         <v>0.00</v>
       </c>
       <c r="P261" s="15" t="n">
-        <v>2425416.39</v>
+        <v>22888437.30</v>
       </c>
     </row>
     <row r="262" spans="1:16" ht="16.5" customHeight="1">
@@ -8799,19 +8817,19 @@
         <v>88</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D264" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="E264" s="16" t="n">
-        <v>0.00</v>
+        <v>847087.63</v>
       </c>
       <c r="F264" s="16" t="n">
-        <v>2987518.24</v>
+        <v>0.00</v>
       </c>
       <c r="G264" s="16" t="n">
         <v>0.00</v>
@@ -8841,7 +8859,7 @@
         <v>0.00</v>
       </c>
       <c r="P264" s="16" t="n">
-        <v>2987518.24</v>
+        <v>847087.63</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="16.5" customHeight="1">
@@ -8885,13 +8903,13 @@
         <v>89</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D267" s="15" t="n">
-        <v>768952.28</v>
+        <v>0.00</v>
       </c>
       <c r="E267" s="15" t="n">
         <v>0.00</v>
@@ -8906,7 +8924,7 @@
         <v>0.00</v>
       </c>
       <c r="I267" s="15" t="n">
-        <v>0.00</v>
+        <v>1131124.74</v>
       </c>
       <c r="J267" s="15" t="n">
         <v>0.00</v>
@@ -8927,7 +8945,7 @@
         <v>0.00</v>
       </c>
       <c r="P267" s="15" t="n">
-        <v>768952.28</v>
+        <v>1131124.74</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="16.5" customHeight="1">
@@ -8971,10 +8989,10 @@
         <v>90</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D270" s="16" t="n">
         <v>0.00</v>
@@ -8989,10 +9007,10 @@
         <v>0.00</v>
       </c>
       <c r="H270" s="16" t="n">
-        <v>0.00</v>
+        <v>2425416.39</v>
       </c>
       <c r="I270" s="16" t="n">
-        <v>2459264.77</v>
+        <v>0.00</v>
       </c>
       <c r="J270" s="16" t="n">
         <v>0.00</v>
@@ -9013,7 +9031,7 @@
         <v>0.00</v>
       </c>
       <c r="P270" s="16" t="n">
-        <v>2459264.77</v>
+        <v>2425416.39</v>
       </c>
     </row>
     <row r="271" spans="1:16" ht="16.5" customHeight="1">
@@ -9057,10 +9075,10 @@
         <v>91</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D273" s="15" t="n">
         <v>0.00</v>
@@ -9069,7 +9087,7 @@
         <v>0.00</v>
       </c>
       <c r="F273" s="15" t="n">
-        <v>0.00</v>
+        <v>2987518.24</v>
       </c>
       <c r="G273" s="15" t="n">
         <v>0.00</v>
@@ -9078,7 +9096,7 @@
         <v>0.00</v>
       </c>
       <c r="I273" s="15" t="n">
-        <v>279805.16</v>
+        <v>0.00</v>
       </c>
       <c r="J273" s="15" t="n">
         <v>0.00</v>
@@ -9099,7 +9117,7 @@
         <v>0.00</v>
       </c>
       <c r="P273" s="15" t="n">
-        <v>279805.16</v>
+        <v>2987518.24</v>
       </c>
     </row>
     <row r="274" spans="1:16" ht="16.5" customHeight="1">
@@ -9143,19 +9161,19 @@
         <v>92</v>
       </c>
       <c r="B276" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D276" s="16" t="n">
-        <v>0.00</v>
+        <v>768952.28</v>
       </c>
       <c r="E276" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="F276" s="16" t="n">
-        <v>1371505.80</v>
+        <v>0.00</v>
       </c>
       <c r="G276" s="16" t="n">
         <v>0.00</v>
@@ -9185,7 +9203,7 @@
         <v>0.00</v>
       </c>
       <c r="P276" s="16" t="n">
-        <v>1371505.80</v>
+        <v>768952.28</v>
       </c>
     </row>
     <row r="277" spans="1:16" ht="16.5" customHeight="1">
@@ -9229,10 +9247,10 @@
         <v>93</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D279" s="15" t="n">
         <v>0.00</v>
@@ -9241,16 +9259,16 @@
         <v>0.00</v>
       </c>
       <c r="F279" s="15" t="n">
-        <v>2132422.07</v>
+        <v>0.00</v>
       </c>
       <c r="G279" s="15" t="n">
-        <v>426484.41</v>
+        <v>0.00</v>
       </c>
       <c r="H279" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="I279" s="15" t="n">
-        <v>1705937.66</v>
+        <v>2459264.77</v>
       </c>
       <c r="J279" s="15" t="n">
         <v>0.00</v>
@@ -9271,7 +9289,7 @@
         <v>0.00</v>
       </c>
       <c r="P279" s="15" t="n">
-        <v>4264844.14</v>
+        <v>2459264.77</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="16.5" customHeight="1">
@@ -9315,13 +9333,13 @@
         <v>94</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D282" s="16" t="n">
-        <v>1329021.15</v>
+        <v>0.00</v>
       </c>
       <c r="E282" s="16" t="n">
         <v>0.00</v>
@@ -9336,7 +9354,7 @@
         <v>0.00</v>
       </c>
       <c r="I282" s="16" t="n">
-        <v>0.00</v>
+        <v>279805.16</v>
       </c>
       <c r="J282" s="16" t="n">
         <v>0.00</v>
@@ -9357,7 +9375,7 @@
         <v>0.00</v>
       </c>
       <c r="P282" s="16" t="n">
-        <v>1329021.15</v>
+        <v>279805.16</v>
       </c>
     </row>
     <row r="283" spans="1:16" ht="16.5" customHeight="1">
@@ -9401,10 +9419,10 @@
         <v>95</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D285" s="15" t="n">
         <v>0.00</v>
@@ -9413,7 +9431,7 @@
         <v>0.00</v>
       </c>
       <c r="F285" s="15" t="n">
-        <v>32195587.93</v>
+        <v>1371505.80</v>
       </c>
       <c r="G285" s="15" t="n">
         <v>0.00</v>
@@ -9443,7 +9461,7 @@
         <v>0.00</v>
       </c>
       <c r="P285" s="15" t="n">
-        <v>32195587.93</v>
+        <v>1371505.80</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="16.5" customHeight="1">
@@ -9487,10 +9505,10 @@
         <v>96</v>
       </c>
       <c r="B288" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D288" s="16" t="n">
         <v>0.00</v>
@@ -9499,16 +9517,16 @@
         <v>0.00</v>
       </c>
       <c r="F288" s="16" t="n">
-        <v>0.00</v>
+        <v>2132422.07</v>
       </c>
       <c r="G288" s="16" t="n">
-        <v>2759019.32</v>
+        <v>426484.41</v>
       </c>
       <c r="H288" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="I288" s="16" t="n">
-        <v>0.00</v>
+        <v>1705937.66</v>
       </c>
       <c r="J288" s="16" t="n">
         <v>0.00</v>
@@ -9529,7 +9547,7 @@
         <v>0.00</v>
       </c>
       <c r="P288" s="16" t="n">
-        <v>2759019.32</v>
+        <v>4264844.14</v>
       </c>
     </row>
     <row r="289" spans="1:16" ht="16.5" customHeight="1">
@@ -9573,16 +9591,16 @@
         <v>97</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D291" s="15" t="n">
-        <v>0.00</v>
+        <v>1329021.15</v>
       </c>
       <c r="E291" s="15" t="n">
-        <v>6277413.55</v>
+        <v>0.00</v>
       </c>
       <c r="F291" s="15" t="n">
         <v>0.00</v>
@@ -9615,7 +9633,7 @@
         <v>0.00</v>
       </c>
       <c r="P291" s="15" t="n">
-        <v>6277413.55</v>
+        <v>1329021.15</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="16.5" customHeight="1">
@@ -9659,10 +9677,10 @@
         <v>98</v>
       </c>
       <c r="B294" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D294" s="16" t="n">
         <v>0.00</v>
@@ -9671,13 +9689,13 @@
         <v>0.00</v>
       </c>
       <c r="F294" s="16" t="n">
-        <v>0.00</v>
+        <v>32195587.93</v>
       </c>
       <c r="G294" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="H294" s="16" t="n">
-        <v>4268792.84</v>
+        <v>0.00</v>
       </c>
       <c r="I294" s="16" t="n">
         <v>0.00</v>
@@ -9701,7 +9719,7 @@
         <v>0.00</v>
       </c>
       <c r="P294" s="16" t="n">
-        <v>4268792.84</v>
+        <v>32195587.93</v>
       </c>
     </row>
     <row r="295" spans="1:16" ht="16.5" customHeight="1">
@@ -9745,13 +9763,13 @@
         <v>99</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D297" s="15" t="n">
-        <v>19218262.50</v>
+        <v>0.00</v>
       </c>
       <c r="E297" s="15" t="n">
         <v>0.00</v>
@@ -9760,7 +9778,7 @@
         <v>0.00</v>
       </c>
       <c r="G297" s="15" t="n">
-        <v>0.00</v>
+        <v>2759019.32</v>
       </c>
       <c r="H297" s="15" t="n">
         <v>0.00</v>
@@ -9787,7 +9805,7 @@
         <v>0.00</v>
       </c>
       <c r="P297" s="15" t="n">
-        <v>19218262.50</v>
+        <v>2759019.32</v>
       </c>
     </row>
     <row r="298" spans="1:16" ht="16.5" customHeight="1">
@@ -9831,19 +9849,19 @@
         <v>100</v>
       </c>
       <c r="B300" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D300" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="E300" s="16" t="n">
-        <v>0.00</v>
+        <v>6277413.55</v>
       </c>
       <c r="F300" s="16" t="n">
-        <v>5523599.87</v>
+        <v>0.00</v>
       </c>
       <c r="G300" s="16" t="n">
         <v>0.00</v>
@@ -9873,7 +9891,7 @@
         <v>0.00</v>
       </c>
       <c r="P300" s="16" t="n">
-        <v>5523599.87</v>
+        <v>6277413.55</v>
       </c>
     </row>
     <row r="301" spans="1:16" ht="16.5" customHeight="1">
@@ -9917,13 +9935,13 @@
         <v>101</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D303" s="15" t="n">
-        <v>1556432.46</v>
+        <v>0.00</v>
       </c>
       <c r="E303" s="15" t="n">
         <v>0.00</v>
@@ -9935,7 +9953,7 @@
         <v>0.00</v>
       </c>
       <c r="H303" s="15" t="n">
-        <v>0.00</v>
+        <v>4268792.84</v>
       </c>
       <c r="I303" s="15" t="n">
         <v>0.00</v>
@@ -9959,7 +9977,7 @@
         <v>0.00</v>
       </c>
       <c r="P303" s="15" t="n">
-        <v>1556432.46</v>
+        <v>4268792.84</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="16.5" customHeight="1">
@@ -10003,13 +10021,13 @@
         <v>102</v>
       </c>
       <c r="B306" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D306" s="16" t="n">
-        <v>0.00</v>
+        <v>19218262.50</v>
       </c>
       <c r="E306" s="16" t="n">
         <v>0.00</v>
@@ -10021,10 +10039,10 @@
         <v>0.00</v>
       </c>
       <c r="H306" s="16" t="n">
-        <v>2361359.74</v>
+        <v>0.00</v>
       </c>
       <c r="I306" s="16" t="n">
-        <v>10232558.86</v>
+        <v>0.00</v>
       </c>
       <c r="J306" s="16" t="n">
         <v>0.00</v>
@@ -10045,7 +10063,7 @@
         <v>0.00</v>
       </c>
       <c r="P306" s="16" t="n">
-        <v>12593918.60</v>
+        <v>19218262.50</v>
       </c>
     </row>
     <row r="307" spans="1:16" ht="16.5" customHeight="1">
@@ -10089,10 +10107,10 @@
         <v>103</v>
       </c>
       <c r="B309" s="11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D309" s="15" t="n">
         <v>0.00</v>
@@ -10101,10 +10119,10 @@
         <v>0.00</v>
       </c>
       <c r="F309" s="15" t="n">
-        <v>0.00</v>
+        <v>5523599.87</v>
       </c>
       <c r="G309" s="15" t="n">
-        <v>31485245.74</v>
+        <v>0.00</v>
       </c>
       <c r="H309" s="15" t="n">
         <v>0.00</v>
@@ -10131,7 +10149,7 @@
         <v>0.00</v>
       </c>
       <c r="P309" s="15" t="n">
-        <v>31485245.74</v>
+        <v>5523599.87</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="16.5" customHeight="1">
@@ -10175,19 +10193,19 @@
         <v>104</v>
       </c>
       <c r="B312" s="12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D312" s="16" t="n">
-        <v>0.00</v>
+        <v>1556432.46</v>
       </c>
       <c r="E312" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="F312" s="16" t="n">
-        <v>27083573.57</v>
+        <v>0.00</v>
       </c>
       <c r="G312" s="16" t="n">
         <v>0.00</v>
@@ -10217,7 +10235,7 @@
         <v>0.00</v>
       </c>
       <c r="P312" s="16" t="n">
-        <v>27083573.57</v>
+        <v>1556432.46</v>
       </c>
     </row>
     <row r="313" spans="1:16" ht="16.5" customHeight="1">
@@ -10261,10 +10279,10 @@
         <v>105</v>
       </c>
       <c r="B315" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D315" s="15" t="n">
         <v>0.00</v>
@@ -10273,16 +10291,16 @@
         <v>0.00</v>
       </c>
       <c r="F315" s="15" t="n">
-        <v>1004599.27</v>
+        <v>0.00</v>
       </c>
       <c r="G315" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="H315" s="15" t="n">
-        <v>0.00</v>
+        <v>2361359.74</v>
       </c>
       <c r="I315" s="15" t="n">
-        <v>0.00</v>
+        <v>13381038.51</v>
       </c>
       <c r="J315" s="15" t="n">
         <v>0.00</v>
@@ -10303,7 +10321,7 @@
         <v>0.00</v>
       </c>
       <c r="P315" s="15" t="n">
-        <v>1004599.27</v>
+        <v>15742398.25</v>
       </c>
     </row>
     <row r="316" spans="1:16" ht="16.5" customHeight="1">
@@ -10347,10 +10365,10 @@
         <v>106</v>
       </c>
       <c r="B318" s="12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D318" s="16" t="n">
         <v>0.00</v>
@@ -10359,10 +10377,10 @@
         <v>0.00</v>
       </c>
       <c r="F318" s="16" t="n">
-        <v>1626262.86</v>
+        <v>0.00</v>
       </c>
       <c r="G318" s="16" t="n">
-        <v>0.00</v>
+        <v>31485245.74</v>
       </c>
       <c r="H318" s="16" t="n">
         <v>0.00</v>
@@ -10389,7 +10407,7 @@
         <v>0.00</v>
       </c>
       <c r="P318" s="16" t="n">
-        <v>1626262.86</v>
+        <v>31485245.74</v>
       </c>
     </row>
     <row r="319" spans="1:16" ht="16.5" customHeight="1">
@@ -10433,10 +10451,10 @@
         <v>107</v>
       </c>
       <c r="B321" s="11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D321" s="15" t="n">
         <v>0.00</v>
@@ -10445,7 +10463,7 @@
         <v>0.00</v>
       </c>
       <c r="F321" s="15" t="n">
-        <v>777981.56</v>
+        <v>27083573.57</v>
       </c>
       <c r="G321" s="15" t="n">
         <v>0.00</v>
@@ -10475,7 +10493,7 @@
         <v>0.00</v>
       </c>
       <c r="P321" s="15" t="n">
-        <v>777981.56</v>
+        <v>27083573.57</v>
       </c>
     </row>
     <row r="322" spans="1:16" ht="16.5" customHeight="1">
@@ -10519,10 +10537,10 @@
         <v>108</v>
       </c>
       <c r="B324" s="12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D324" s="16" t="n">
         <v>0.00</v>
@@ -10531,10 +10549,10 @@
         <v>0.00</v>
       </c>
       <c r="F324" s="16" t="n">
-        <v>0.00</v>
+        <v>1004599.27</v>
       </c>
       <c r="G324" s="16" t="n">
-        <v>82174.71</v>
+        <v>0.00</v>
       </c>
       <c r="H324" s="16" t="n">
         <v>0.00</v>
@@ -10561,7 +10579,7 @@
         <v>0.00</v>
       </c>
       <c r="P324" s="16" t="n">
-        <v>82174.71</v>
+        <v>1004599.27</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="16.5" customHeight="1">
@@ -10605,10 +10623,10 @@
         <v>109</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D327" s="15" t="n">
         <v>0.00</v>
@@ -10617,13 +10635,13 @@
         <v>0.00</v>
       </c>
       <c r="F327" s="15" t="n">
-        <v>0.00</v>
+        <v>1626262.86</v>
       </c>
       <c r="G327" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="H327" s="15" t="n">
-        <v>17728563.67</v>
+        <v>0.00</v>
       </c>
       <c r="I327" s="15" t="n">
         <v>0.00</v>
@@ -10647,7 +10665,7 @@
         <v>0.00</v>
       </c>
       <c r="P327" s="15" t="n">
-        <v>17728563.67</v>
+        <v>1626262.86</v>
       </c>
     </row>
     <row r="328" spans="1:16" ht="16.5" customHeight="1">
@@ -10691,10 +10709,10 @@
         <v>110</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D330" s="16" t="n">
         <v>0.00</v>
@@ -10703,13 +10721,13 @@
         <v>0.00</v>
       </c>
       <c r="F330" s="16" t="n">
-        <v>147696743.79</v>
+        <v>777981.56</v>
       </c>
       <c r="G330" s="16" t="n">
-        <v>88049981.88</v>
+        <v>0.00</v>
       </c>
       <c r="H330" s="16" t="n">
-        <v>20288014.26</v>
+        <v>0.00</v>
       </c>
       <c r="I330" s="16" t="n">
         <v>0.00</v>
@@ -10733,7 +10751,7 @@
         <v>0.00</v>
       </c>
       <c r="P330" s="16" t="n">
-        <v>256034739.93</v>
+        <v>777981.56</v>
       </c>
     </row>
     <row r="331" spans="1:16" ht="16.5" customHeight="1">
@@ -10777,28 +10795,28 @@
         <v>111</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D333" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="E333" s="15" t="n">
-        <v>115400411.78</v>
+        <v>0.00</v>
       </c>
       <c r="F333" s="15" t="n">
-        <v>69513825.63</v>
+        <v>0.00</v>
       </c>
       <c r="G333" s="15" t="n">
-        <v>58819390.92</v>
+        <v>82174.71</v>
       </c>
       <c r="H333" s="15" t="n">
-        <v>23627239.48</v>
+        <v>0.00</v>
       </c>
       <c r="I333" s="15" t="n">
-        <v>17782606.56</v>
+        <v>0.00</v>
       </c>
       <c r="J333" s="15" t="n">
         <v>0.00</v>
@@ -10819,7 +10837,7 @@
         <v>0.00</v>
       </c>
       <c r="P333" s="15" t="n">
-        <v>285143474.37</v>
+        <v>82174.71</v>
       </c>
     </row>
     <row r="334" spans="1:16" ht="16.5" customHeight="1">
@@ -10863,25 +10881,25 @@
         <v>112</v>
       </c>
       <c r="B336" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D336" s="16" t="n">
-        <v>7065872.89</v>
+        <v>0.00</v>
       </c>
       <c r="E336" s="16" t="n">
         <v>0.00</v>
       </c>
       <c r="F336" s="16" t="n">
-        <v>5130336.75</v>
+        <v>0.00</v>
       </c>
       <c r="G336" s="16" t="n">
-        <v>5596731.00</v>
+        <v>0.00</v>
       </c>
       <c r="H336" s="16" t="n">
-        <v>0.00</v>
+        <v>17728563.67</v>
       </c>
       <c r="I336" s="16" t="n">
         <v>0.00</v>
@@ -10905,7 +10923,7 @@
         <v>0.00</v>
       </c>
       <c r="P336" s="16" t="n">
-        <v>17792940.64</v>
+        <v>17728563.67</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="16.5" customHeight="1">
@@ -10949,25 +10967,25 @@
         <v>113</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D339" s="15" t="n">
-        <v>11989806.77</v>
+        <v>0.00</v>
       </c>
       <c r="E339" s="15" t="n">
         <v>0.00</v>
       </c>
       <c r="F339" s="15" t="n">
-        <v>18042913.11</v>
+        <v>147696743.79</v>
       </c>
       <c r="G339" s="15" t="n">
-        <v>0.00</v>
+        <v>88049981.88</v>
       </c>
       <c r="H339" s="15" t="n">
-        <v>0.00</v>
+        <v>20288014.26</v>
       </c>
       <c r="I339" s="15" t="n">
         <v>0.00</v>
@@ -10991,7 +11009,7 @@
         <v>0.00</v>
       </c>
       <c r="P339" s="15" t="n">
-        <v>30032719.88</v>
+        <v>256034739.93</v>
       </c>
     </row>
     <row r="340" spans="1:16" ht="16.5" customHeight="1">
@@ -11035,28 +11053,28 @@
         <v>114</v>
       </c>
       <c r="B342" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D342" s="16" t="n">
-        <v>38850000.00</v>
+        <v>0.00</v>
       </c>
       <c r="E342" s="16" t="n">
-        <v>0.00</v>
+        <v>115400411.78</v>
       </c>
       <c r="F342" s="16" t="n">
-        <v>0.00</v>
+        <v>69513825.63</v>
       </c>
       <c r="G342" s="16" t="n">
-        <v>0.00</v>
+        <v>58819390.92</v>
       </c>
       <c r="H342" s="16" t="n">
-        <v>0.00</v>
+        <v>23627239.48</v>
       </c>
       <c r="I342" s="16" t="n">
-        <v>0.00</v>
+        <v>37306167.60</v>
       </c>
       <c r="J342" s="16" t="n">
         <v>0.00</v>
@@ -11077,7 +11095,7 @@
         <v>0.00</v>
       </c>
       <c r="P342" s="16" t="n">
-        <v>38850000.00</v>
+        <v>304667035.41</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="16.5" customHeight="1">
@@ -11099,90 +11117,348 @@
       <c r="P343" s="7"/>
     </row>
     <row r="344" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A344" s="8"/>
-      <c r="B344" s="8"/>
-      <c r="C344" s="8"/>
-      <c r="D344" s="8"/>
-      <c r="E344" s="8"/>
-      <c r="F344" s="8"/>
-      <c r="G344" s="8"/>
-      <c r="H344" s="8"/>
-      <c r="I344" s="8"/>
-      <c r="J344" s="8"/>
-      <c r="K344" s="8"/>
-      <c r="L344" s="8"/>
-      <c r="M344" s="8"/>
-      <c r="N344" s="8"/>
-      <c r="O344" s="8"/>
-      <c r="P344" s="8"/>
+      <c r="A344" s="2"/>
+      <c r="B344" s="2"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
+      <c r="E344" s="2"/>
+      <c r="F344" s="2"/>
+      <c r="G344" s="2"/>
+      <c r="H344" s="2"/>
+      <c r="I344" s="2"/>
+      <c r="J344" s="2"/>
+      <c r="K344" s="2"/>
+      <c r="L344" s="2"/>
+      <c r="M344" s="2"/>
+      <c r="N344" s="2"/>
+      <c r="O344" s="2"/>
+      <c r="P344" s="2"/>
     </row>
     <row r="345" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A345" s="9" t="s">
+      <c r="A345" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B345" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="C345" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D345" s="17" t="n">
+      <c r="B345" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D345" s="15" t="n">
+        <v>7065872.89</v>
+      </c>
+      <c r="E345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="F345" s="15" t="n">
+        <v>5130336.75</v>
+      </c>
+      <c r="G345" s="15" t="n">
+        <v>5596731.00</v>
+      </c>
+      <c r="H345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="I345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="J345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="K345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="L345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="M345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="N345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="O345" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="P345" s="15" t="n">
+        <v>17792940.64</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A346" s="4"/>
+      <c r="B346" s="4"/>
+      <c r="C346" s="4"/>
+      <c r="D346" s="4"/>
+      <c r="E346" s="4"/>
+      <c r="F346" s="4"/>
+      <c r="G346" s="4"/>
+      <c r="H346" s="4"/>
+      <c r="I346" s="4"/>
+      <c r="J346" s="4"/>
+      <c r="K346" s="4"/>
+      <c r="L346" s="4"/>
+      <c r="M346" s="4"/>
+      <c r="N346" s="4"/>
+      <c r="O346" s="4"/>
+      <c r="P346" s="4"/>
+    </row>
+    <row r="347" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A347" s="5"/>
+      <c r="B347" s="5"/>
+      <c r="C347" s="5"/>
+      <c r="D347" s="5"/>
+      <c r="E347" s="5"/>
+      <c r="F347" s="5"/>
+      <c r="G347" s="5"/>
+      <c r="H347" s="5"/>
+      <c r="I347" s="5"/>
+      <c r="J347" s="5"/>
+      <c r="K347" s="5"/>
+      <c r="L347" s="5"/>
+      <c r="M347" s="5"/>
+      <c r="N347" s="5"/>
+      <c r="O347" s="5"/>
+      <c r="P347" s="5"/>
+    </row>
+    <row r="348" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A348" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D348" s="16" t="n">
+        <v>11989806.77</v>
+      </c>
+      <c r="E348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="F348" s="16" t="n">
+        <v>18042913.11</v>
+      </c>
+      <c r="G348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="H348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="I348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="J348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="K348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="L348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="M348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="N348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="O348" s="16" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="P348" s="16" t="n">
+        <v>30032719.88</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A349" s="7"/>
+      <c r="B349" s="7"/>
+      <c r="C349" s="7"/>
+      <c r="D349" s="7"/>
+      <c r="E349" s="7"/>
+      <c r="F349" s="7"/>
+      <c r="G349" s="7"/>
+      <c r="H349" s="7"/>
+      <c r="I349" s="7"/>
+      <c r="J349" s="7"/>
+      <c r="K349" s="7"/>
+      <c r="L349" s="7"/>
+      <c r="M349" s="7"/>
+      <c r="N349" s="7"/>
+      <c r="O349" s="7"/>
+      <c r="P349" s="7"/>
+    </row>
+    <row r="350" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A350" s="2"/>
+      <c r="B350" s="2"/>
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
+      <c r="E350" s="2"/>
+      <c r="F350" s="2"/>
+      <c r="G350" s="2"/>
+      <c r="H350" s="2"/>
+      <c r="I350" s="2"/>
+      <c r="J350" s="2"/>
+      <c r="K350" s="2"/>
+      <c r="L350" s="2"/>
+      <c r="M350" s="2"/>
+      <c r="N350" s="2"/>
+      <c r="O350" s="2"/>
+      <c r="P350" s="2"/>
+    </row>
+    <row r="351" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A351" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B351" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D351" s="15" t="n">
+        <v>38850000.00</v>
+      </c>
+      <c r="E351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="F351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="G351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="H351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="I351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="J351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="K351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="L351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="M351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="N351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="O351" s="15" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="P351" s="15" t="n">
+        <v>38850000.00</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A352" s="4"/>
+      <c r="B352" s="4"/>
+      <c r="C352" s="4"/>
+      <c r="D352" s="4"/>
+      <c r="E352" s="4"/>
+      <c r="F352" s="4"/>
+      <c r="G352" s="4"/>
+      <c r="H352" s="4"/>
+      <c r="I352" s="4"/>
+      <c r="J352" s="4"/>
+      <c r="K352" s="4"/>
+      <c r="L352" s="4"/>
+      <c r="M352" s="4"/>
+      <c r="N352" s="4"/>
+      <c r="O352" s="4"/>
+      <c r="P352" s="4"/>
+    </row>
+    <row r="353" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A353" s="8"/>
+      <c r="B353" s="8"/>
+      <c r="C353" s="8"/>
+      <c r="D353" s="8"/>
+      <c r="E353" s="8"/>
+      <c r="F353" s="8"/>
+      <c r="G353" s="8"/>
+      <c r="H353" s="8"/>
+      <c r="I353" s="8"/>
+      <c r="J353" s="8"/>
+      <c r="K353" s="8"/>
+      <c r="L353" s="8"/>
+      <c r="M353" s="8"/>
+      <c r="N353" s="8"/>
+      <c r="O353" s="8"/>
+      <c r="P353" s="8"/>
+    </row>
+    <row r="354" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A354" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B354" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C354" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D354" s="17" t="n">
         <v>296337054.51</v>
       </c>
-      <c r="E345" s="17" t="n">
+      <c r="E354" s="17" t="n">
         <v>603238348.69</v>
       </c>
-      <c r="F345" s="17" t="n">
+      <c r="F354" s="17" t="n">
         <v>386632082.27</v>
       </c>
-      <c r="G345" s="17" t="n">
+      <c r="G354" s="17" t="n">
         <v>323263650.85</v>
       </c>
-      <c r="H345" s="17" t="n">
+      <c r="H354" s="17" t="n">
         <v>161742999.22</v>
       </c>
-      <c r="I345" s="17" t="n">
-        <v>54035424.84</v>
-      </c>
-      <c r="J345" s="17" t="n">
-        <v>0.00</v>
-      </c>
-      <c r="K345" s="17" t="n">
-        <v>0.00</v>
-      </c>
-      <c r="L345" s="17" t="n">
-        <v>0.00</v>
-      </c>
-      <c r="M345" s="17" t="n">
-        <v>0.00</v>
-      </c>
-      <c r="N345" s="17" t="n">
-        <v>0.00</v>
-      </c>
-      <c r="O345" s="17" t="n">
-        <v>0.00</v>
-      </c>
-      <c r="P345" s="17" t="n">
-        <v>1825249560.38</v>
-      </c>
-    </row>
-    <row r="346" spans="1:16" ht="16.5" customHeight="1">
-      <c r="A346" s="10"/>
-      <c r="B346" s="10"/>
-      <c r="C346" s="10"/>
-      <c r="D346" s="10"/>
-      <c r="E346" s="10"/>
-      <c r="F346" s="10"/>
-      <c r="G346" s="10"/>
-      <c r="H346" s="10"/>
-      <c r="I346" s="10"/>
-      <c r="J346" s="10"/>
-      <c r="K346" s="10"/>
-      <c r="L346" s="10"/>
-      <c r="M346" s="10"/>
-      <c r="N346" s="10"/>
-      <c r="O346" s="10"/>
-      <c r="P346" s="10"/>
+      <c r="I354" s="17" t="n">
+        <v>83661263.64</v>
+      </c>
+      <c r="J354" s="17" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="K354" s="17" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="L354" s="17" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="M354" s="17" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="N354" s="17" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="O354" s="17" t="n">
+        <v>0.00</v>
+      </c>
+      <c r="P354" s="17" t="n">
+        <v>1854875399.18</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A355" s="10"/>
+      <c r="B355" s="10"/>
+      <c r="C355" s="10"/>
+      <c r="D355" s="10"/>
+      <c r="E355" s="10"/>
+      <c r="F355" s="10"/>
+      <c r="G355" s="10"/>
+      <c r="H355" s="10"/>
+      <c r="I355" s="10"/>
+      <c r="J355" s="10"/>
+      <c r="K355" s="10"/>
+      <c r="L355" s="10"/>
+      <c r="M355" s="10"/>
+      <c r="N355" s="10"/>
+      <c r="O355" s="10"/>
+      <c r="P355" s="10"/>
     </row>
   </sheetData>
 </worksheet>
